--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>73415.60000000001</v>
+        <v>72646.78</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20704.55</v>
+        <v>20850.68</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30447.88</v>
+        <v>30662.76</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29460.92</v>
+        <v>29080.12</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20619.69</v>
+        <v>20381.06</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>54014.19</v>
+        <v>54083.43</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>23816.27</v>
+        <v>23769.37</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46948.8</v>
+        <v>47375.83</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>59771.17</v>
+        <v>61507.31</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31993.75</v>
+        <v>32521.06</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19782.54</v>
+        <v>19799.58</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36488.9</v>
+        <v>35961.01</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>42586.07</v>
+        <v>41669.84</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23076.81</v>
+        <v>22580.31</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21557.37</v>
+        <v>21620.12</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>39361.41</v>
+        <v>39801.61</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>65299.55</v>
+        <v>65919.94</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12940.3</v>
+        <v>13036.7</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>33143.32</v>
+        <v>32998.04</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>41398.65</v>
+        <v>41217.18</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17885.04</v>
+        <v>17941.96</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>35934.53</v>
+        <v>36048.9</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>69364.61</v>
+        <v>70015.2</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14154.85</v>
+        <v>13953.96</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>35276.11</v>
+        <v>35455.87</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1192.86</v>
+        <v>1198.94</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>52378.42</v>
+        <v>52582.32</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>229-1011-CM25</t>
+          <t>4594-20-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,22 +524,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,32 +554,28 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>72646.78</v>
+        <v>24757.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2129-336-CM25</t>
+          <t>1036569-103-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -634,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20850.68</v>
+        <v>26461.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2129-337-CM25</t>
+          <t>1030177-43-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -665,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -695,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30662.76</v>
+        <v>17139.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3671-111-CM25</t>
+          <t>229-372-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -711,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -756,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29080.12</v>
+        <v>24987.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1052231-117-CM25</t>
+          <t>1493-560-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.140.800-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42056.86</v>
+        <v>33887.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1030177-162-CM25</t>
+          <t>4328-640-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -878,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20381.06</v>
+        <v>11504.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3671-123-CM25</t>
+          <t>4329-586-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -909,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>54083.43</v>
+        <v>12995.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4329-23-CM26</t>
+          <t>4594-637-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>23769.37</v>
+        <v>25303.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3671-14-CM26</t>
+          <t>1040758-78-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>47375.83</v>
+        <v>32712.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2724-132-CM26</t>
+          <t>4329-597-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>61507.31</v>
+        <v>21837.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3659-166-CM26</t>
+          <t>1047296-116-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>62.000.460-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>Delegación Presidencial Provincial de Itata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>32521.06</v>
+        <v>19943.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2129-67-CM26</t>
+          <t>1051425-97-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19799.58</v>
+        <v>35723.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5615-169-CM26</t>
+          <t>4121-85-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35961.01</v>
+        <v>29574.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3904-196-CM26</t>
+          <t>1063487-18-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>41669.84</v>
+        <v>26136.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2129-83-CM26</t>
+          <t>4328-867-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>22580.31</v>
+        <v>12637.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4328-330-CM26</t>
+          <t>4328-866-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1463,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,28 +1484,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21620.12</v>
+        <v>20800.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3784-245-CM26</t>
+          <t>3784-2924-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1534,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,28 +1545,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>39801.61</v>
+        <v>50781.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4328-458-CM26</t>
+          <t>2129-256-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,43 +1606,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>65919.94</v>
+        <v>20558.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4252-138-CM26</t>
+          <t>1051425-105-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Cecor S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.010.151-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13036.7</v>
+        <v>42740.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1030177-74-CM26</t>
+          <t>229-1011-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,43 +1713,47 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>32998.04</v>
+        <v>72646.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4252-141-CM26</t>
+          <t>2129-337-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,43 +1793,43 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>41217.18</v>
+        <v>30662.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3594-332-CM26</t>
+          <t>2129-336-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.140.200-2</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,28 +1854,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17941.96</v>
+        <v>20850.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3594-334-CM26</t>
+          <t>1052231-117-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.140.200-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36048.9</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4121-53-CM26</t>
+          <t>3671-111-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,43 +1976,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>70015.2</v>
+        <v>29080.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3784-296-CM26</t>
+          <t>1030177-162-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,28 +2037,28 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>13953.96</v>
+        <v>20381.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2724-529-CM26</t>
+          <t>3671-123-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,28 +2098,28 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>35455.87</v>
+        <v>54083.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2724-530-CM26</t>
+          <t>4329-23-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE NIQUEN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,28 +2159,28 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1198.94</v>
+        <v>23769.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1030177-106-CM26</t>
+          <t>3671-14-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,7 +2220,1288 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
+        <v>47375.83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2724-132-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>61507.31</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3659-166-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>32521.06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2129-67-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.150.300-3</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Ranquil</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>19799.58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5615-169-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.141.700-K</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I.Municipalidad de El Carmen</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>35961.01</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3904-196-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>POMPEYO CARRASCO SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>41669.84</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2129-83-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.150.300-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Ranquil</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>22580.31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4328-330-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.140.600-8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NIQUEN</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>21620.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3784-245-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.150.200-7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>39801.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4328-458-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.140.600-8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NIQUEN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>65919.94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4252-138-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.140.700-4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>13036.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1030177-74-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>32998.04</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4252-141-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.140.700-4</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>41217.18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3594-332-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.140.200-2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>17941.96</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3594-334-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.140.200-2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>36048.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4121-53-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>70015.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3784-296-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.150.200-7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>13953.96</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2724-529-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>35455.87</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2724-530-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1198.94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1030177-106-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>52582.32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3659-742-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>33492.34</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1036569-128-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>83.019.900-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>46798.67</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4594-637-CM25</t>
+          <t>1040758-78-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25303.29</v>
+        <v>32712.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1040758-78-CM25</t>
+          <t>4594-637-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>32712.67</v>
+        <v>25303.29</v>
       </c>
     </row>
     <row r="11">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4328-867-CM25</t>
+          <t>4328-866-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12637.46</v>
+        <v>20800.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4328-866-CM25</t>
+          <t>4328-867-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>20800.91</v>
+        <v>12637.46</v>
       </c>
     </row>
     <row r="18">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3671-123-CM25</t>
+          <t>1375761-114-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>54083.43</v>
+        <v>25643.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4329-23-CM26</t>
+          <t>3671-123-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>23769.37</v>
+        <v>54083.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3671-14-CM26</t>
+          <t>4329-23-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>47375.83</v>
+        <v>23769.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2724-132-CM26</t>
+          <t>3671-14-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,27 +2236,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>61507.31</v>
+        <v>47375.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3659-166-CM26</t>
+          <t>2724-132-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,22 +2302,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>32521.06</v>
+        <v>61507.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2129-67-CM26</t>
+          <t>3659-166-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19799.58</v>
+        <v>32521.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5615-169-CM26</t>
+          <t>2129-67-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>35961.01</v>
+        <v>19799.58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3904-196-CM26</t>
+          <t>5615-169-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41669.84</v>
+        <v>35961.01</v>
       </c>
     </row>
     <row r="35">
@@ -2592,22 +2592,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4328-330-CM26</t>
+          <t>3904-196-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>21620.12</v>
+        <v>41669.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3784-245-CM26</t>
+          <t>4328-330-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,27 +2663,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>39801.61</v>
+        <v>21620.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4328-458-CM26</t>
+          <t>3784-245-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,22 +2729,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>65919.94</v>
+        <v>39801.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4252-138-CM26</t>
+          <t>4328-458-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>13036.7</v>
+        <v>65919.94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1030177-74-CM26</t>
+          <t>4252-138-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>32998.04</v>
+        <v>13036.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4252-141-CM26</t>
+          <t>1030177-74-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41217.18</v>
+        <v>32998.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3594-332-CM26</t>
+          <t>4252-141-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.140.200-2</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>17941.96</v>
+        <v>41217.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3594-334-CM26</t>
+          <t>3594-332-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>36048.9</v>
+        <v>17941.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4121-53-CM26</t>
+          <t>3594-334-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,27 +3090,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.140.200-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>70015.2</v>
+        <v>36048.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3784-296-CM26</t>
+          <t>4121-53-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>13953.96</v>
+        <v>70015.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2724-529-CM26</t>
+          <t>3784-296-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,27 +3212,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>35455.87</v>
+        <v>13953.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2724-530-CM26</t>
+          <t>2724-529-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1198.94</v>
+        <v>35455.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1030177-106-CM26</t>
+          <t>2724-530-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>52582.32</v>
+        <v>1198.94</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3659-742-CM26</t>
+          <t>1030177-106-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>33492.34</v>
+        <v>52582.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1036569-128-CM26</t>
+          <t>3659-742-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>83.019.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,7 +3501,255 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
+        <v>33492.34</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1036569-128-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>83.019.900-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
         <v>46798.67</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2705-1399-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.911.006-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>192227.18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2724-878-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>47745.65</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2724-879-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>734.5599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
@@ -562,7 +562,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1850,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1915,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1980,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2045,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2110,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2175,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2240,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2370,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2435,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2500,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2565,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2630,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2695,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2760,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2825,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2890,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3016,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3081,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3207,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3272,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3459,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3524,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3650,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3681,7 +3841,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3906,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -969,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1040758-78-CM25</t>
+          <t>4594-637-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32712.67</v>
+        <v>25303.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4594-637-CM25</t>
+          <t>1040758-78-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>25303.29</v>
+        <v>32712.67</v>
       </c>
     </row>
     <row r="11">
@@ -1420,7 +1420,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4328-866-CM25</t>
+          <t>4328-867-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1460,28 +1460,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20800.91</v>
+        <v>12637.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4328-867-CM25</t>
+          <t>4328-866-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1521,26 +1525,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12637.46</v>
+        <v>20800.91</v>
       </c>
     </row>
     <row r="18">
@@ -1802,7 +1802,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2129-337-CM25</t>
+          <t>2129-336-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1842,17 +1842,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>30662.76</v>
+        <v>20850.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2129-336-CM25</t>
+          <t>2129-337-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20850.68</v>
+        <v>30662.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1052231-117-CM25</t>
+          <t>3671-111-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1991,13 +1991,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>42056.86</v>
+        <v>29080.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3671-111-CM25</t>
+          <t>1052231-117-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29080.12</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="26">
@@ -3411,7 +3411,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2724-529-CM26</t>
+          <t>2724-530-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>35455.87</v>
+        <v>1198.94</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2724-530-CM26</t>
+          <t>2724-529-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1198.94</v>
+        <v>35455.87</v>
       </c>
     </row>
     <row r="49">
@@ -3793,7 +3793,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2724-878-CM26</t>
+          <t>2724-879-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3852,13 +3852,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>47745.65</v>
+        <v>734.5599999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2724-879-CM26</t>
+          <t>2724-878-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3917,7 +3917,198 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>734.5599999999999</v>
+        <v>47745.65</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>5041-50-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>237987.31</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1180937-20-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.607.000-2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>33478.81</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5615-602-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.141.700-K</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de El Carmen</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>35388.62</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/nuble.xlsx
@@ -3431,7 +3431,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
